--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487119_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487119_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2349</v>
+        <v>4.7863</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1734</v>
+        <v>5.6713</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9385</v>
+        <v>-0.885</v>
       </c>
       <c r="G2" t="n">
         <v>2.5374</v>
@@ -610,13 +610,13 @@
         <v>0.386</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2765</v>
+        <v>0.8279</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5805</v>
+        <v>1.0784</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3041</v>
+        <v>-0.2505</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0929</v>
+        <v>4.5004</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5687</v>
+        <v>4.6282</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4757</v>
+        <v>-0.1277</v>
       </c>
       <c r="G3" t="n">
         <v>6.1815</v>
@@ -688,13 +688,13 @@
         <v>0.772</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8692</v>
+        <v>1.2767</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9188</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0496</v>
+        <v>0.2984</v>
       </c>
       <c r="V3" t="n">
         <v>-1.7997</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5111</v>
+        <v>3.9569</v>
       </c>
       <c r="E4" t="n">
-        <v>3.89</v>
+        <v>4.325</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3789</v>
+        <v>-0.3681</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0564</v>
+        <v>3.4849</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7026</v>
+        <v>1.0723</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6462</v>
+        <v>2.4127</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7754</v>
+        <v>3.1982</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4023</v>
+        <v>2.5148</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6269</v>
+        <v>0.6833</v>
       </c>
       <c r="M4" t="n">
-        <v>0.281</v>
+        <v>0.2868</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3002</v>
+        <v>-1.4426</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0193</v>
+        <v>1.7293</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1966</v>
+        <v>1.7229</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1146</v>
+        <v>1.2149</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0819</v>
+        <v>0.5079</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5138</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9089</v>
+        <v>2.1063</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4644</v>
+        <v>2.7947</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5555</v>
+        <v>-0.6884</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4849</v>
+        <v>1.4739</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0723</v>
+        <v>-0.1997</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4127</v>
+        <v>1.6737</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1982</v>
+        <v>2.0204</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5148</v>
+        <v>0.1811</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6833</v>
+        <v>1.8393</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2868</v>
+        <v>-0.5464</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4426</v>
+        <v>-0.3808</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7293</v>
+        <v>-0.1657</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.965</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-3.0881</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6749000000000001</v>
+        <v>1.1065</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3543</v>
+        <v>0.7925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3205</v>
+        <v>0.3139</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>1.842</v>
       </c>
       <c r="W5" t="n">
-        <v>1.842</v>
+        <v>3.0699</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1278</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4018</v>
+        <v>2.0625</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3991</v>
+        <v>2.3879</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8009</v>
+        <v>-0.3254</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8753</v>
+        <v>1.0564</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2274</v>
+        <v>1.7026</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6479</v>
+        <v>-0.6462</v>
       </c>
       <c r="J6" t="n">
-        <v>2.528</v>
+        <v>0.7754</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7954</v>
+        <v>1.4023</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7326</v>
+        <v>-0.6269</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3474</v>
+        <v>0.281</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.3002</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9154</v>
+        <v>-0.0193</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.0881</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5567</v>
+        <v>1.748</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4965</v>
+        <v>1.6125</v>
       </c>
       <c r="U6" t="n">
-        <v>2.0602</v>
+        <v>0.1355</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9421</v>
+        <v>-1.5138</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5717</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1584</v>
+        <v>1.6454</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7933</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6349</v>
+        <v>2.1852</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4739</v>
+        <v>2.8753</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1997</v>
+        <v>1.2274</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6737</v>
+        <v>1.6479</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0204</v>
+        <v>2.528</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1811</v>
+        <v>1.7954</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8393</v>
+        <v>0.7326</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5464</v>
+        <v>0.3474</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3808</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1657</v>
+        <v>0.9154</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3161</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0881</v>
+        <v>-4.0532</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1586</v>
+        <v>2.8003</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2089</v>
+        <v>1.3557</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3675</v>
+        <v>1.4445</v>
       </c>
       <c r="V7" t="n">
-        <v>1.842</v>
+        <v>-0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>3.0699</v>
+        <v>-0.3704</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2925</v>
+        <v>0.3539</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.665</v>
+        <v>-0.8044</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3724</v>
+        <v>1.1583</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6383</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3881</v>
+        <v>2.0345</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4733</v>
+        <v>1.3339</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.7006</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0422</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2524</v>
+        <v>-0.8786</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0299</v>
+        <v>0.3707</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2226</v>
+        <v>-1.2493</v>
       </c>
       <c r="G9" t="n">
         <v>1.0658</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0324</v>
+        <v>0.3414</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>0.1626</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2056</v>
+        <v>0.1788</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5138</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2665</v>
+        <v>-1.4921</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.744</v>
+        <v>-2.1838</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4775</v>
+        <v>0.6917</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6967</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1838</v>
+        <v>0.5906</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>0.1438</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2327</v>
+        <v>0.4468</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7429</v>
+        <v>-2.779</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1363</v>
+        <v>-1.1648</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6066</v>
+        <v>-1.6142</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5946</v>
+        <v>1.1616</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7192</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3138</v>
+        <v>0.1742</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2079</v>
+        <v>1.6083</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0866</v>
+        <v>1.0143</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2945</v>
+        <v>0.5941</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3866</v>
+        <v>-0.4467</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3674</v>
+        <v>-0.0268</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0193</v>
+        <v>-0.4199</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.6672</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.0532</v>
+        <v>-2.8951</v>
       </c>
       <c r="R11" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4609</v>
+        <v>-0.0106</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8389</v>
+        <v>0.122</v>
       </c>
       <c r="U11" t="n">
-        <v>0.622</v>
+        <v>-0.1325</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9421</v>
+        <v>-1.228</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-1.228</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3204</v>
+        <v>-3.4707</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4653</v>
+        <v>-2.8373</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8551</v>
+        <v>-0.6334</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1616</v>
+        <v>-0.5946</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.7192</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1742</v>
+        <v>-1.3138</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6083</v>
+        <v>-0.2079</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0143</v>
+        <v>1.0866</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5941</v>
+        <v>-1.2945</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4467</v>
+        <v>-0.3866</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0268</v>
+        <v>-0.3674</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4199</v>
+        <v>-0.0193</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7021</v>
+        <v>-3.6672</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>-4.0532</v>
       </c>
       <c r="R12" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5518999999999999</v>
+        <v>1.7331</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1785</v>
+        <v>1.1379</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3735</v>
+        <v>0.5952</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.228</v>
+        <v>-0.9421</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
         <v>-1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9122</v>
+        <v>-3.9727</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6152</v>
+        <v>-1.5151</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.297</v>
+        <v>-2.4576</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5871</v>
@@ -1468,13 +1468,13 @@
         <v>0.579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5169</v>
+        <v>0.4564</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5632</v>
+        <v>0.6633</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0463</v>
+        <v>-0.2069</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.521099999999997</v>
+        <v>6.8186</v>
       </c>
       <c r="E14" t="n">
-        <v>10.835</v>
+        <v>11.1326</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.314</v>
+        <v>-4.3139</v>
       </c>
       <c r="G14" t="n">
         <v>14.3201</v>
@@ -1534,7 +1534,7 @@
         <v>-6.679600000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>5.179999999999999</v>
+        <v>5.18</v>
       </c>
       <c r="P14" t="n">
         <v>-14.4755</v>
@@ -1546,19 +1546,19 @@
         <v>7.72</v>
       </c>
       <c r="S14" t="n">
-        <v>14.3303</v>
+        <v>14.6277</v>
       </c>
       <c r="T14" t="n">
-        <v>10.2983</v>
+        <v>10.5958</v>
       </c>
       <c r="U14" t="n">
-        <v>4.031700000000001</v>
+        <v>4.0317</v>
       </c>
       <c r="V14" t="n">
         <v>-7.653500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.913</v>
+        <v>6.912999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-14.5666</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6487</v>
+        <v>4.1807</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7957</v>
+        <v>5.1949</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.147</v>
+        <v>-1.0142</v>
       </c>
       <c r="G15" t="n">
         <v>1.6268</v>
@@ -1624,13 +1624,13 @@
         <v>4.0532</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.515</v>
+        <v>-1.983</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0543</v>
+        <v>-0.5466</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5692</v>
+        <v>-1.4364</v>
       </c>
       <c r="V15" t="n">
         <v>2.4137</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RUIZ VICENTE</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1732</v>
+        <v>1.7683</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1092</v>
+        <v>1.1462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.064</v>
+        <v>0.6221</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4137</v>
+        <v>-6.2041</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1397</v>
+        <v>-2.2685</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5534</v>
+        <v>-3.9356</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3293</v>
+        <v>-4.3149</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7437</v>
+        <v>-0.3985</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5855</v>
+        <v>-3.9164</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9156</v>
+        <v>-1.8893</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8834</v>
+        <v>-1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0321</v>
+        <v>-0.0193</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>3.6672</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2811</v>
+        <v>3.6672</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2056</v>
+        <v>-2.1204</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1383</v>
+        <v>-0.9647</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3438</v>
+        <v>-1.1558</v>
       </c>
       <c r="V16" t="n">
-        <v>0.614</v>
+        <v>6.4257</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5717</v>
+        <v>6.4257</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>A. RUIZ VICENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6664</v>
+        <v>1.0978</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4452</v>
+        <v>1.0077</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2212</v>
+        <v>0.0901</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.2041</v>
+        <v>0.4137</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2685</v>
+        <v>-0.1397</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.9356</v>
+        <v>0.5534</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.3149</v>
+        <v>2.3293</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3985</v>
+        <v>1.7437</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.9164</v>
+        <v>0.5855</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8893</v>
+        <v>-1.9156</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.87</v>
+        <v>-1.8834</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0193</v>
+        <v>-0.0321</v>
       </c>
       <c r="P17" t="n">
-        <v>3.6672</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6672</v>
+        <v>3.2811</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.2223</v>
+        <v>-1.281</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6657</v>
+        <v>0.0367</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5567</v>
+        <v>-1.3177</v>
       </c>
       <c r="V17" t="n">
-        <v>6.4257</v>
+        <v>0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>6.4257</v>
+        <v>0.5717</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0877</v>
+        <v>-0.0609</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0181</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0696</v>
+        <v>-0.0428</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2391</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0416</v>
+        <v>-0.0149</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8743</v>
+        <v>-1.6138</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7487</v>
+        <v>-0.6486</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1255</v>
+        <v>-0.9653</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2332</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2201</v>
+        <v>0.0403</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1639</v>
+        <v>-0.0638</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0562</v>
+        <v>0.1041</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3737</v>
+        <v>-2.115</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9993</v>
+        <v>-0.3853</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3744</v>
+        <v>-1.7297</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2511</v>
+        <v>-0.6486</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4189</v>
+        <v>-2.6786</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1678</v>
+        <v>2.03</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5234</v>
+        <v>0.8401</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5641</v>
+        <v>-0.9421</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>1.7822</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7277</v>
+        <v>-1.4887</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8548</v>
+        <v>-1.7365</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1271</v>
+        <v>0.2478</v>
       </c>
       <c r="P20" t="n">
         <v>0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>3.8602</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1878</v>
+        <v>-2.7173</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4759</v>
+        <v>-1.0721</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7119</v>
+        <v>-1.6452</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8999</v>
+        <v>0.2859</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7418</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8999</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8097</v>
+        <v>-2.1397</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7859</v>
+        <v>-0.8992</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0238</v>
+        <v>-1.2406</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6486</v>
+        <v>-1.2511</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6786</v>
+        <v>-1.4189</v>
       </c>
       <c r="I21" t="n">
-        <v>2.03</v>
+        <v>0.1678</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8401</v>
+        <v>-0.5234</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9421</v>
+        <v>-0.5641</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7822</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4887</v>
+        <v>-0.7277</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7365</v>
+        <v>-0.8548</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2478</v>
+        <v>0.1271</v>
       </c>
       <c r="P21" t="n">
         <v>0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.8602</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.412</v>
+        <v>-0.9538</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4726</v>
+        <v>-0.3758</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.9394</v>
+        <v>-0.578</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2859</v>
+        <v>-0.8999</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4559</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2231</v>
+        <v>-2.3856</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6058</v>
+        <v>-0.0772</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6173</v>
+        <v>-2.3084</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1285</v>
+        <v>-2.6561</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2285</v>
+        <v>-0.7968</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9</v>
+        <v>-1.8593</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1926</v>
+        <v>0.2606</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6881</v>
+        <v>1.5472</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8807</v>
+        <v>-1.2866</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9359</v>
+        <v>-2.9167</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9166</v>
+        <v>-2.344</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0193</v>
+        <v>-0.5727</v>
       </c>
       <c r="P22" t="n">
-        <v>0.965</v>
+        <v>3.6672</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9301</v>
+        <v>3.6672</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1019</v>
+        <v>-2.1687</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3239</v>
+        <v>-0.9095</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4258</v>
+        <v>-1.2592</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0422</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
-        <v>1.228</v>
+        <v>0.5717</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1857</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6408</v>
+        <v>-3.2499</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8783</v>
+        <v>-1.0063</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7625</v>
+        <v>-2.2435</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6561</v>
+        <v>-3.1285</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7968</v>
+        <v>-1.2285</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8593</v>
+        <v>-1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2606</v>
+        <v>-1.1926</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5472</v>
+        <v>0.6881</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2866</v>
+        <v>-1.8807</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9167</v>
+        <v>-1.9359</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.344</v>
+        <v>-1.9166</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5727</v>
+        <v>-0.0193</v>
       </c>
       <c r="P23" t="n">
-        <v>3.6672</v>
+        <v>0.965</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>3.6672</v>
+        <v>1.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.4239</v>
+        <v>-1.1286</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7106</v>
+        <v>-0.0766</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7133</v>
+        <v>-1.052</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.228</v>
+        <v>0.0422</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5717</v>
+        <v>1.228</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.521000000000001</v>
+        <v>-4.518099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>4.313999999999998</v>
+        <v>4.3141</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.8349</v>
+        <v>-8.8323</v>
       </c>
       <c r="G24" t="n">
         <v>-14.3202</v>
@@ -2302,7 +2302,7 @@
         <v>1.4995</v>
       </c>
       <c r="K24" t="n">
-        <v>6.679500000000001</v>
+        <v>6.6795</v>
       </c>
       <c r="L24" t="n">
         <v>-5.180099999999999</v>
@@ -2323,16 +2323,16 @@
         <v>-7.7203</v>
       </c>
       <c r="R24" t="n">
-        <v>22.19600000000001</v>
+        <v>22.196</v>
       </c>
       <c r="S24" t="n">
-        <v>-14.3302</v>
+        <v>-12.3274</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.031699999999999</v>
+        <v>-4.031899999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-10.2985</v>
+        <v>-8.2956</v>
       </c>
       <c r="V24" t="n">
         <v>7.653600000000001</v>
@@ -2341,7 +2341,7 @@
         <v>14.5666</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.913</v>
+        <v>-6.912999999999999</v>
       </c>
     </row>
   </sheetData>
